--- a/Owl/docs/绩效评分-测试事业部-产品研发部-崔永元.xlsx
+++ b/Owl/docs/绩效评分-测试事业部-产品研发部-崔永元.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Constantine-Projects\Owl\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDAEC69-04C5-4FB7-A087-171E9B74A5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96113D81-BF42-4EEE-A1A7-0B2F732CE76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{FB500AD7-6AA8-4603-8490-B7888ED23A0A}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="95">
   <si>
     <t>个人目标管理卡</t>
   </si>
@@ -1439,33 +1439,25 @@
       <c r="F15" s="6"/>
       <c r="H15" s="20"/>
     </row>
-    <row r="16" spans="2:15" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="37" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="15">
-        <v>8.5</v>
-      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="16"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="2:8" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="37"/>
       <c r="C17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="15">
-        <v>8.5</v>
-      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="16"/>
       <c r="H17" s="21"/>
     </row>
@@ -1620,32 +1612,24 @@
       </c>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="2:8" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="37" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="15">
-        <v>8.5</v>
-      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="2:8" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="37"/>
       <c r="C29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="15">
-        <v>8.5</v>
-      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="16"/>
     </row>
     <row r="30" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,32 +1765,24 @@
       </c>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:8" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="15">
-        <v>8.5</v>
-      </c>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="2:8" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="40"/>
       <c r="C41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="15">
-        <v>8.5</v>
-      </c>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="16"/>
     </row>
     <row r="42" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
